--- a/Results_experiment/exp_5/preds_1114422222322222.xlsx
+++ b/Results_experiment/exp_5/preds_1114422222322222.xlsx
@@ -1245,7 +1245,7 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>1.391624689102173</v>
+        <v>1.213574767112732</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1259,7 +1259,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D3">
-        <v>2.09731912612915</v>
+        <v>2.001261711120605</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>2.102302074432373</v>
+        <v>1.291074514389038</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1287,7 +1287,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D5">
-        <v>1.822450041770935</v>
+        <v>1.77664852142334</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1301,7 +1301,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D6">
-        <v>1.562495708465576</v>
+        <v>1.533987283706665</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1315,7 +1315,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D7">
-        <v>2.782397270202637</v>
+        <v>1.922704458236694</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1329,7 +1329,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D8">
-        <v>4.656608104705811</v>
+        <v>3.69420599937439</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1343,7 +1343,7 @@
         <v>4.5</v>
       </c>
       <c r="D9">
-        <v>2.051399707794189</v>
+        <v>1.742754936218262</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1357,7 +1357,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D10">
-        <v>1.093544960021973</v>
+        <v>1.157276391983032</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1371,7 +1371,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D11">
-        <v>2.13141918182373</v>
+        <v>2.8364098072052</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1385,7 +1385,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D12">
-        <v>0.8428788185119629</v>
+        <v>0.78788822889328</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1399,7 +1399,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D13">
-        <v>1.436882257461548</v>
+        <v>1.224600195884705</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1413,7 +1413,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D14">
-        <v>1.149349808692932</v>
+        <v>1.271875381469727</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1427,7 +1427,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D15">
-        <v>2.773128509521484</v>
+        <v>2.397110223770142</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1441,7 +1441,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D16">
-        <v>2.435465097427368</v>
+        <v>2.728249788284302</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1455,7 +1455,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D17">
-        <v>2.150509357452393</v>
+        <v>2.700489521026611</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1469,7 +1469,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D18">
-        <v>0.9995147585868835</v>
+        <v>1.192905426025391</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1483,7 +1483,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D19">
-        <v>2.212970733642578</v>
+        <v>1.683703899383545</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1497,7 +1497,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D20">
-        <v>2.552059650421143</v>
+        <v>1.817138195037842</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1511,7 +1511,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D21">
-        <v>1.179514169692993</v>
+        <v>0.816028892993927</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1525,7 +1525,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D22">
-        <v>3.966140747070312</v>
+        <v>3.479790210723877</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1539,7 +1539,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D23">
-        <v>2.913134574890137</v>
+        <v>2.71157431602478</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1553,7 +1553,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D24">
-        <v>3.124906539916992</v>
+        <v>2.619205951690674</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1567,7 +1567,7 @@
         <v>0.5</v>
       </c>
       <c r="D25">
-        <v>2.207191944122314</v>
+        <v>2.040868520736694</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1581,7 +1581,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D26">
-        <v>2.960719585418701</v>
+        <v>2.662885665893555</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1595,7 +1595,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D27">
-        <v>2.17821216583252</v>
+        <v>2.377451181411743</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1609,7 +1609,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D28">
-        <v>1.130560398101807</v>
+        <v>1.325409531593323</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1623,7 +1623,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D29">
-        <v>1.544189214706421</v>
+        <v>0.8492461442947388</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1637,7 +1637,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D30">
-        <v>1.508206129074097</v>
+        <v>1.316494464874268</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1651,7 +1651,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D31">
-        <v>3.705495834350586</v>
+        <v>2.974506378173828</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1665,7 +1665,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D32">
-        <v>4.777632713317871</v>
+        <v>4.196526527404785</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1679,7 +1679,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D33">
-        <v>1.042973041534424</v>
+        <v>2.211366891860962</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1693,7 +1693,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D34">
-        <v>0.8506686091423035</v>
+        <v>0.8013755679130554</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1707,7 +1707,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D35">
-        <v>1.100244522094727</v>
+        <v>1.282034397125244</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1721,7 +1721,7 @@
         <v>19.20000076293945</v>
       </c>
       <c r="D36">
-        <v>12.21920776367188</v>
+        <v>15.80296325683594</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1735,7 +1735,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D37">
-        <v>2.054662466049194</v>
+        <v>2.080619096755981</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1749,7 +1749,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D38">
-        <v>2.274942874908447</v>
+        <v>2.459090948104858</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1763,7 +1763,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D39">
-        <v>3.374251842498779</v>
+        <v>3.044908761978149</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1777,7 +1777,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D40">
-        <v>1.161524057388306</v>
+        <v>1.056406497955322</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1791,7 +1791,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D41">
-        <v>1.081446170806885</v>
+        <v>1.255768775939941</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1805,7 +1805,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D42">
-        <v>3.393690586090088</v>
+        <v>3.31346583366394</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1819,7 +1819,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D43">
-        <v>0.8233058452606201</v>
+        <v>0.7860051989555359</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1833,7 +1833,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D44">
-        <v>2.641414403915405</v>
+        <v>3.307747364044189</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1847,7 +1847,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D45">
-        <v>1.174776554107666</v>
+        <v>1.326858282089233</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1861,7 +1861,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D46">
-        <v>2.829309463500977</v>
+        <v>2.420408248901367</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1875,7 +1875,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D47">
-        <v>1.044027209281921</v>
+        <v>1.297588586807251</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1889,7 +1889,7 @@
         <v>3.5</v>
       </c>
       <c r="D48">
-        <v>3.408712387084961</v>
+        <v>2.276746988296509</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1903,7 +1903,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D49">
-        <v>2.331985712051392</v>
+        <v>2.963865756988525</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1917,7 +1917,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D50">
-        <v>3.630453586578369</v>
+        <v>3.304681539535522</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1931,7 +1931,7 @@
         <v>2</v>
       </c>
       <c r="D51">
-        <v>1.113885641098022</v>
+        <v>1.36869740486145</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1945,7 +1945,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D52">
-        <v>1.25836980342865</v>
+        <v>1.094327449798584</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1959,7 +1959,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>1.034883141517639</v>
+        <v>0.8473064303398132</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1973,7 +1973,7 @@
         <v>2.5</v>
       </c>
       <c r="D54">
-        <v>2.159660816192627</v>
+        <v>2.242111921310425</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1987,7 +1987,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D55">
-        <v>1.990843296051025</v>
+        <v>1.307985782623291</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2001,7 +2001,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D56">
-        <v>1.841963887214661</v>
+        <v>2.092729330062866</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2015,7 +2015,7 @@
         <v>10.19999980926514</v>
       </c>
       <c r="D57">
-        <v>8.261513710021973</v>
+        <v>7.432991027832031</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2029,7 +2029,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D58">
-        <v>1.133412837982178</v>
+        <v>2.223614692687988</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2043,7 +2043,7 @@
         <v>2.5</v>
       </c>
       <c r="D59">
-        <v>1.115260481834412</v>
+        <v>1.359723329544067</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2057,7 +2057,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D60">
-        <v>4.902122020721436</v>
+        <v>4.92082691192627</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2071,7 +2071,7 @@
         <v>0.5</v>
       </c>
       <c r="D61">
-        <v>1.090107679367065</v>
+        <v>1.242608904838562</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2085,7 +2085,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D62">
-        <v>6.556399345397949</v>
+        <v>5.786690711975098</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2099,7 +2099,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D63">
-        <v>1.39553689956665</v>
+        <v>1.3360915184021</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2113,7 +2113,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D64">
-        <v>0.8963780403137207</v>
+        <v>1.090561032295227</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2127,7 +2127,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D65">
-        <v>1.367719650268555</v>
+        <v>0.8150988817214966</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2141,7 +2141,7 @@
         <v>1.5</v>
       </c>
       <c r="D66">
-        <v>2.194735527038574</v>
+        <v>2.201392889022827</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2155,7 +2155,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D67">
-        <v>2.852742195129395</v>
+        <v>3.020141363143921</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2169,7 +2169,7 @@
         <v>5.5</v>
       </c>
       <c r="D68">
-        <v>2.458999633789062</v>
+        <v>3.02944016456604</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2183,7 +2183,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D69">
-        <v>1.071787118911743</v>
+        <v>0.9589845538139343</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2197,7 +2197,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D70">
-        <v>2.19939661026001</v>
+        <v>2.552372694015503</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2211,7 +2211,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D71">
-        <v>2.29262113571167</v>
+        <v>1.162242293357849</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2225,7 +2225,7 @@
         <v>3.5</v>
       </c>
       <c r="D72">
-        <v>4.424953937530518</v>
+        <v>3.689301490783691</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2239,7 +2239,7 @@
         <v>1</v>
       </c>
       <c r="D73">
-        <v>1.453882455825806</v>
+        <v>1.345962285995483</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2253,7 +2253,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D74">
-        <v>1.654674291610718</v>
+        <v>2.348556995391846</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2267,7 +2267,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D75">
-        <v>5.676987648010254</v>
+        <v>4.897463798522949</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2281,7 +2281,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D76">
-        <v>1.181215763092041</v>
+        <v>1.302899599075317</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2295,7 +2295,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D77">
-        <v>2.435566425323486</v>
+        <v>2.399121761322021</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2309,7 +2309,7 @@
         <v>2</v>
       </c>
       <c r="D78">
-        <v>2.79992151260376</v>
+        <v>2.200414657592773</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2323,7 +2323,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D79">
-        <v>3.456581115722656</v>
+        <v>3.076401948928833</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2337,7 +2337,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D80">
-        <v>1.97495424747467</v>
+        <v>2.512488842010498</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2351,7 +2351,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>2.361932277679443</v>
+        <v>3.38264012336731</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2365,7 +2365,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D82">
-        <v>1.098689079284668</v>
+        <v>1.24158501625061</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2379,7 +2379,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D83">
-        <v>2.628444194793701</v>
+        <v>2.664047956466675</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2393,7 +2393,7 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>5.529030323028564</v>
+        <v>3.026782989501953</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2407,7 +2407,7 @@
         <v>21</v>
       </c>
       <c r="D85">
-        <v>14.87806701660156</v>
+        <v>14.83796119689941</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2421,7 +2421,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D86">
-        <v>1.855205416679382</v>
+        <v>1.727629423141479</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2435,7 +2435,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D87">
-        <v>1.061149716377258</v>
+        <v>0.9583307504653931</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2449,7 +2449,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D88">
-        <v>3.518184185028076</v>
+        <v>3.248749017715454</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2463,7 +2463,7 @@
         <v>3</v>
       </c>
       <c r="D89">
-        <v>2.117650032043457</v>
+        <v>2.093294620513916</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2477,7 +2477,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D90">
-        <v>1.531298160552979</v>
+        <v>1.834690809249878</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2491,7 +2491,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D91">
-        <v>1.116398930549622</v>
+        <v>1.355005741119385</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2505,7 +2505,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D92">
-        <v>2.469526767730713</v>
+        <v>1.324810981750488</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2519,7 +2519,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D93">
-        <v>1.116945743560791</v>
+        <v>0.9183023571968079</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2533,7 +2533,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D94">
-        <v>1.123257875442505</v>
+        <v>1.345828294754028</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2547,7 +2547,7 @@
         <v>2</v>
       </c>
       <c r="D95">
-        <v>1.796444892883301</v>
+        <v>1.41259765625</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2561,7 +2561,7 @@
         <v>1.5</v>
       </c>
       <c r="D96">
-        <v>1.049742698669434</v>
+        <v>0.7985747456550598</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2575,7 +2575,7 @@
         <v>3</v>
       </c>
       <c r="D97">
-        <v>3.327594757080078</v>
+        <v>2.624774932861328</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2589,7 +2589,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D98">
-        <v>1.667421340942383</v>
+        <v>0.9549006223678589</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2603,7 +2603,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D99">
-        <v>0.8966723680496216</v>
+        <v>0.8012711405754089</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2617,7 +2617,7 @@
         <v>0.5</v>
       </c>
       <c r="D100">
-        <v>0.8278099298477173</v>
+        <v>0.7927065491676331</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2631,7 +2631,7 @@
         <v>1.5</v>
       </c>
       <c r="D101">
-        <v>0.82024085521698</v>
+        <v>0.9049460887908936</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2645,7 +2645,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D102">
-        <v>2.717848062515259</v>
+        <v>2.662159442901611</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2659,7 +2659,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D103">
-        <v>8.045121192932129</v>
+        <v>6.350518226623535</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2673,7 +2673,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D104">
-        <v>4.765235424041748</v>
+        <v>4.21944522857666</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2687,7 +2687,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D105">
-        <v>2.810073375701904</v>
+        <v>2.353581190109253</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2701,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="D106">
-        <v>2.113326549530029</v>
+        <v>2.109787702560425</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2715,7 +2715,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D107">
-        <v>1.253597855567932</v>
+        <v>1.469325065612793</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2729,7 +2729,7 @@
         <v>2.5</v>
       </c>
       <c r="D108">
-        <v>2.10089635848999</v>
+        <v>2.50245189666748</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2743,7 +2743,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D109">
-        <v>3.159463405609131</v>
+        <v>2.727713108062744</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2757,7 +2757,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D110">
-        <v>4.327239036560059</v>
+        <v>3.490591764450073</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2771,7 +2771,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D111">
-        <v>2.250259399414062</v>
+        <v>2.006044864654541</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2785,7 +2785,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D112">
-        <v>1.056905746459961</v>
+        <v>1.329316377639771</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2799,7 +2799,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D113">
-        <v>1.024358749389648</v>
+        <v>1.240629434585571</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2813,7 +2813,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D114">
-        <v>2.24048900604248</v>
+        <v>2.205446481704712</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2827,7 +2827,7 @@
         <v>0.5</v>
       </c>
       <c r="D115">
-        <v>1.026486039161682</v>
+        <v>0.8134713172912598</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2841,7 +2841,7 @@
         <v>2</v>
       </c>
       <c r="D116">
-        <v>1.094975113868713</v>
+        <v>1.273739814758301</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2855,7 +2855,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D117">
-        <v>1.222416520118713</v>
+        <v>0.8338501453399658</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2869,7 +2869,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D118">
-        <v>3.499919891357422</v>
+        <v>3.155663728713989</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2883,7 +2883,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D119">
-        <v>1.064203143119812</v>
+        <v>0.8033556342124939</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2897,7 +2897,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D120">
-        <v>1.012006998062134</v>
+        <v>0.8047611117362976</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2911,7 +2911,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D121">
-        <v>0.9599560499191284</v>
+        <v>1.262063264846802</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2925,7 +2925,7 @@
         <v>17.10000038146973</v>
       </c>
       <c r="D122">
-        <v>6.969215393066406</v>
+        <v>5.200071811676025</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2939,7 +2939,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D123">
-        <v>1.473299741744995</v>
+        <v>0.8365238904953003</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2953,7 +2953,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D124">
-        <v>1.371951937675476</v>
+        <v>1.445137023925781</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2967,7 +2967,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D125">
-        <v>2.101820468902588</v>
+        <v>2.456759214401245</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2981,7 +2981,7 @@
         <v>18.29999923706055</v>
       </c>
       <c r="D126">
-        <v>11.79494857788086</v>
+        <v>12.09589862823486</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2995,7 +2995,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D127">
-        <v>1.915694355964661</v>
+        <v>2.453023433685303</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3009,7 +3009,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D128">
-        <v>1.437532782554626</v>
+        <v>1.288486838340759</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3023,7 +3023,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D129">
-        <v>1.906512379646301</v>
+        <v>1.843233585357666</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3037,7 +3037,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D130">
-        <v>2.066296100616455</v>
+        <v>1.991924047470093</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3051,7 +3051,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D131">
-        <v>1.087746143341064</v>
+        <v>1.208005547523499</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3065,7 +3065,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D132">
-        <v>1.86968195438385</v>
+        <v>2.739861011505127</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3079,7 +3079,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D133">
-        <v>2.382519245147705</v>
+        <v>3.209099054336548</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3093,7 +3093,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D134">
-        <v>0.8207518458366394</v>
+        <v>0.7800624966621399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3107,7 +3107,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D135">
-        <v>3.220229625701904</v>
+        <v>2.580069065093994</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3121,7 +3121,7 @@
         <v>17.29999923706055</v>
       </c>
       <c r="D136">
-        <v>5.014366626739502</v>
+        <v>4.617210388183594</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3135,7 +3135,7 @@
         <v>2.5</v>
       </c>
       <c r="D137">
-        <v>2.257022857666016</v>
+        <v>2.34113621711731</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3149,7 +3149,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D138">
-        <v>0.8241387605667114</v>
+        <v>0.9935628175735474</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3163,7 +3163,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D139">
-        <v>3.579746723175049</v>
+        <v>3.216104745864868</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3177,7 +3177,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D140">
-        <v>1.310293197631836</v>
+        <v>1.749322652816772</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3191,7 +3191,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D141">
-        <v>2.90227222442627</v>
+        <v>2.982300281524658</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3205,7 +3205,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D142">
-        <v>3.170787811279297</v>
+        <v>3.045870065689087</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3219,7 +3219,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D143">
-        <v>2.403353691101074</v>
+        <v>2.070477724075317</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3233,7 +3233,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D144">
-        <v>0.9865351915359497</v>
+        <v>0.8163617849349976</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3247,7 +3247,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D145">
-        <v>1.044939398765564</v>
+        <v>1.289485454559326</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3261,7 +3261,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D146">
-        <v>1.082217693328857</v>
+        <v>1.284601449966431</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3275,7 +3275,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D147">
-        <v>2.675019979476929</v>
+        <v>2.837731122970581</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3289,7 +3289,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D148">
-        <v>2.286340236663818</v>
+        <v>2.509321689605713</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3303,7 +3303,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D149">
-        <v>1.814155697822571</v>
+        <v>1.462320327758789</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3317,7 +3317,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D150">
-        <v>2.087652206420898</v>
+        <v>2.419809341430664</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3331,7 +3331,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D151">
-        <v>2.371309041976929</v>
+        <v>2.426752805709839</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3345,7 +3345,7 @@
         <v>11</v>
       </c>
       <c r="D152">
-        <v>6.799578666687012</v>
+        <v>7.114791870117188</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3359,7 +3359,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D153">
-        <v>1.958643317222595</v>
+        <v>2.276181221008301</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3373,7 +3373,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D154">
-        <v>2.155154228210449</v>
+        <v>2.138330936431885</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3387,7 +3387,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D155">
-        <v>0.8241121768951416</v>
+        <v>1.300758123397827</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3401,7 +3401,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D156">
-        <v>1.038691282272339</v>
+        <v>1.3107750415802</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3415,7 +3415,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D157">
-        <v>3.412880420684814</v>
+        <v>2.590444326400757</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3429,7 +3429,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D158">
-        <v>2.992122173309326</v>
+        <v>2.708558320999146</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3443,7 +3443,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D159">
-        <v>1.92949903011322</v>
+        <v>1.68980860710144</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3457,7 +3457,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D160">
-        <v>2.045995712280273</v>
+        <v>2.341181993484497</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3471,7 +3471,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D161">
-        <v>1.314651012420654</v>
+        <v>1.8563072681427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3485,7 +3485,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D162">
-        <v>7.933922290802002</v>
+        <v>2.219509124755859</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3499,7 +3499,7 @@
         <v>1.5</v>
       </c>
       <c r="D163">
-        <v>2.576994657516479</v>
+        <v>2.319211721420288</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3513,7 +3513,7 @@
         <v>0.5</v>
       </c>
       <c r="D164">
-        <v>1.174889087677002</v>
+        <v>2.189529418945312</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3527,7 +3527,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D165">
-        <v>0.8135360479354858</v>
+        <v>1.842296600341797</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3541,7 +3541,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D166">
-        <v>2.593778133392334</v>
+        <v>2.393442630767822</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3555,7 +3555,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D167">
-        <v>2.340863704681396</v>
+        <v>2.475924730300903</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3569,7 +3569,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D168">
-        <v>2.157211780548096</v>
+        <v>2.232331991195679</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3583,7 +3583,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D169">
-        <v>0.8632403612136841</v>
+        <v>0.9620534777641296</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3597,7 +3597,7 @@
         <v>6</v>
       </c>
       <c r="D170">
-        <v>2.186427593231201</v>
+        <v>2.29624605178833</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3611,7 +3611,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D171">
-        <v>2.018335819244385</v>
+        <v>2.611690282821655</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3625,7 +3625,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D172">
-        <v>1.229812383651733</v>
+        <v>0.8339447975158691</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3639,7 +3639,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D173">
-        <v>2.937354564666748</v>
+        <v>2.327839612960815</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3653,7 +3653,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D174">
-        <v>1.598490118980408</v>
+        <v>1.907860517501831</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3667,7 +3667,7 @@
         <v>2.5</v>
       </c>
       <c r="D175">
-        <v>3.289451122283936</v>
+        <v>3.01587700843811</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3681,7 +3681,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D176">
-        <v>0.8372970819473267</v>
+        <v>0.8456132411956787</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3695,7 +3695,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D177">
-        <v>2.136563777923584</v>
+        <v>2.643806934356689</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3709,7 +3709,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D178">
-        <v>1.481242537498474</v>
+        <v>1.413558483123779</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3723,7 +3723,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D179">
-        <v>3.444680690765381</v>
+        <v>2.457876205444336</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3737,7 +3737,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D180">
-        <v>2.119888782501221</v>
+        <v>2.044203281402588</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3751,7 +3751,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D181">
-        <v>0.94197016954422</v>
+        <v>0.797580897808075</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3765,7 +3765,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D182">
-        <v>2.518661499023438</v>
+        <v>2.522871732711792</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3779,7 +3779,7 @@
         <v>0.5</v>
       </c>
       <c r="D183">
-        <v>1.311748504638672</v>
+        <v>1.172124981880188</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3793,7 +3793,7 @@
         <v>5</v>
       </c>
       <c r="D184">
-        <v>2.183372020721436</v>
+        <v>1.99485969543457</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3807,7 +3807,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D185">
-        <v>1.676296234130859</v>
+        <v>1.425314664840698</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3821,7 +3821,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D186">
-        <v>1.097491979598999</v>
+        <v>1.083470106124878</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3835,7 +3835,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D187">
-        <v>1.050583720207214</v>
+        <v>0.8350580930709839</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3849,7 +3849,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D188">
-        <v>2.177931308746338</v>
+        <v>2.114499568939209</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3863,7 +3863,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D189">
-        <v>1.635207653045654</v>
+        <v>1.599889874458313</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3877,7 +3877,7 @@
         <v>6</v>
       </c>
       <c r="D190">
-        <v>2.840780735015869</v>
+        <v>3.410676002502441</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3891,7 +3891,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D191">
-        <v>4.202959537506104</v>
+        <v>3.462280988693237</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3905,7 +3905,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D192">
-        <v>1.22519063949585</v>
+        <v>1.111053586006165</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3919,7 +3919,7 @@
         <v>1.5</v>
       </c>
       <c r="D193">
-        <v>1.693134307861328</v>
+        <v>2.289297580718994</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3933,7 +3933,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D194">
-        <v>2.905416488647461</v>
+        <v>2.913853883743286</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3947,7 +3947,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D195">
-        <v>2.855559825897217</v>
+        <v>2.479182243347168</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3961,7 +3961,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D196">
-        <v>2.207329988479614</v>
+        <v>2.455964326858521</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3975,7 +3975,7 @@
         <v>6.5</v>
       </c>
       <c r="D197">
-        <v>1.174961924552917</v>
+        <v>2.195315361022949</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3989,7 +3989,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D198">
-        <v>3.620765209197998</v>
+        <v>3.331660032272339</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>1.085462689399719</v>
+        <v>1.293972015380859</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4017,7 +4017,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D200">
-        <v>1.078951835632324</v>
+        <v>0.8434954881668091</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4031,7 +4031,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D201">
-        <v>1.97344958782196</v>
+        <v>1.808521032333374</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4045,7 +4045,7 @@
         <v>5.5</v>
       </c>
       <c r="D202">
-        <v>4.104681491851807</v>
+        <v>2.523752212524414</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4059,7 +4059,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D203">
-        <v>0.8615452647209167</v>
+        <v>1.92730188369751</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4073,7 +4073,7 @@
         <v>1.5</v>
       </c>
       <c r="D204">
-        <v>3.358246803283691</v>
+        <v>2.650056838989258</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4087,7 +4087,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D205">
-        <v>4.025207996368408</v>
+        <v>2.623452186584473</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4101,7 +4101,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D206">
-        <v>1.072933673858643</v>
+        <v>0.8577882647514343</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4115,7 +4115,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D207">
-        <v>3.032907962799072</v>
+        <v>3.26257061958313</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4129,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="D208">
-        <v>1.036032438278198</v>
+        <v>1.299464225769043</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4143,7 +4143,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D209">
-        <v>1.660773873329163</v>
+        <v>1.58432936668396</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4157,7 +4157,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D210">
-        <v>1.132121205329895</v>
+        <v>1.347399473190308</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4171,7 +4171,7 @@
         <v>2</v>
       </c>
       <c r="D211">
-        <v>2.785385131835938</v>
+        <v>2.71753978729248</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4185,7 +4185,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D212">
-        <v>5.012115955352783</v>
+        <v>5.314956188201904</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4199,7 +4199,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D213">
-        <v>2.070405960083008</v>
+        <v>1.904570341110229</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4213,7 +4213,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D214">
-        <v>3.258015155792236</v>
+        <v>2.992187261581421</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4227,7 +4227,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D215">
-        <v>2.894884586334229</v>
+        <v>2.808634757995605</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4241,7 +4241,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D216">
-        <v>3.119184494018555</v>
+        <v>3.512739658355713</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4255,7 +4255,7 @@
         <v>9</v>
       </c>
       <c r="D217">
-        <v>3.633031845092773</v>
+        <v>3.84341835975647</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4269,7 +4269,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D218">
-        <v>3.805923461914062</v>
+        <v>3.242626190185547</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4283,7 +4283,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D219">
-        <v>3.543521404266357</v>
+        <v>3.119110345840454</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4297,7 +4297,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D220">
-        <v>1.904502511024475</v>
+        <v>2.165854454040527</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4311,7 +4311,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D221">
-        <v>1.092196464538574</v>
+        <v>1.403755903244019</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4325,7 +4325,7 @@
         <v>3.5</v>
       </c>
       <c r="D222">
-        <v>1.256432890892029</v>
+        <v>1.543037891387939</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4339,7 +4339,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D223">
-        <v>1.414906144142151</v>
+        <v>0.9961387515068054</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4353,7 +4353,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D224">
-        <v>2.494162559509277</v>
+        <v>2.678679227828979</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4367,7 +4367,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D225">
-        <v>1.192619562149048</v>
+        <v>1.233356595039368</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4381,7 +4381,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D226">
-        <v>0.949263870716095</v>
+        <v>0.9122607111930847</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4395,7 +4395,7 @@
         <v>3.5</v>
       </c>
       <c r="D227">
-        <v>2.252025127410889</v>
+        <v>2.228823661804199</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4409,7 +4409,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D228">
-        <v>2.483812808990479</v>
+        <v>2.174622774124146</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4423,7 +4423,7 @@
         <v>11</v>
       </c>
       <c r="D229">
-        <v>4.962696552276611</v>
+        <v>5.691793918609619</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4437,7 +4437,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D230">
-        <v>3.044085502624512</v>
+        <v>2.213934183120728</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4451,7 +4451,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D231">
-        <v>2.149108171463013</v>
+        <v>2.085683584213257</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4465,7 +4465,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D232">
-        <v>1.671288013458252</v>
+        <v>2.069244146347046</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4479,7 +4479,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D233">
-        <v>1.085692286491394</v>
+        <v>0.8243712186813354</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4493,7 +4493,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D234">
-        <v>2.428804874420166</v>
+        <v>2.536120653152466</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4507,7 +4507,7 @@
         <v>0.5</v>
       </c>
       <c r="D235">
-        <v>2.623683452606201</v>
+        <v>2.173877954483032</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4521,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="D236">
-        <v>2.065192699432373</v>
+        <v>1.650986552238464</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4535,7 +4535,7 @@
         <v>0.5</v>
       </c>
       <c r="D237">
-        <v>0.9622762203216553</v>
+        <v>0.8859399557113647</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4549,7 +4549,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D238">
-        <v>2.235363006591797</v>
+        <v>2.330891132354736</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4563,7 +4563,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D239">
-        <v>3.77705717086792</v>
+        <v>2.872488975524902</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4577,7 +4577,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D240">
-        <v>3.71372127532959</v>
+        <v>3.241533517837524</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4591,7 +4591,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D241">
-        <v>3.551954746246338</v>
+        <v>3.763015508651733</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4605,7 +4605,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D242">
-        <v>3.321310520172119</v>
+        <v>2.619607925415039</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4619,7 +4619,7 @@
         <v>3.5</v>
       </c>
       <c r="D243">
-        <v>2.117296695709229</v>
+        <v>2.198149919509888</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4633,7 +4633,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D244">
-        <v>2.564573764801025</v>
+        <v>2.665667772293091</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4647,7 +4647,7 @@
         <v>2</v>
       </c>
       <c r="D245">
-        <v>1.27960991859436</v>
+        <v>0.8435885906219482</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4661,7 +4661,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D246">
-        <v>3.562453746795654</v>
+        <v>3.094173669815063</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>0.8135360479354858</v>
+        <v>0.8257224559783936</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4689,7 +4689,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D248">
-        <v>3.817106246948242</v>
+        <v>3.326902389526367</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4703,7 +4703,7 @@
         <v>20.5</v>
       </c>
       <c r="D249">
-        <v>1.066555738449097</v>
+        <v>0.8108533024787903</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4717,7 +4717,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D250">
-        <v>3.800802230834961</v>
+        <v>2.670719861984253</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4731,7 +4731,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D251">
-        <v>3.283737182617188</v>
+        <v>2.703337669372559</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4745,7 +4745,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D252">
-        <v>2.20458984375</v>
+        <v>2.27871561050415</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4759,7 +4759,7 @@
         <v>1</v>
       </c>
       <c r="D253">
-        <v>3.155681610107422</v>
+        <v>2.870847702026367</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4773,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="D254">
-        <v>1.21747624874115</v>
+        <v>0.8306823968887329</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4787,7 +4787,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D255">
-        <v>2.456991672515869</v>
+        <v>2.463130474090576</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4801,7 +4801,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D256">
-        <v>4.762977123260498</v>
+        <v>3.87860894203186</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4815,7 +4815,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D257">
-        <v>1.669063568115234</v>
+        <v>1.739210605621338</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4829,7 +4829,7 @@
         <v>10.5</v>
       </c>
       <c r="D258">
-        <v>3.588497638702393</v>
+        <v>3.100528001785278</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4843,7 +4843,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D259">
-        <v>2.784668922424316</v>
+        <v>2.592021703720093</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4857,7 +4857,7 @@
         <v>1.5</v>
       </c>
       <c r="D260">
-        <v>2.650044918060303</v>
+        <v>2.148421764373779</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4871,7 +4871,7 @@
         <v>0.5</v>
       </c>
       <c r="D261">
-        <v>1.110073208808899</v>
+        <v>1.113580346107483</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4885,7 +4885,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D262">
-        <v>1.316121459007263</v>
+        <v>1.325391292572021</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4899,7 +4899,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D263">
-        <v>1.58230459690094</v>
+        <v>0.8423920273780823</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4913,7 +4913,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D264">
-        <v>1.042810440063477</v>
+        <v>0.9923518300056458</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4927,7 +4927,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D265">
-        <v>1.932113528251648</v>
+        <v>2.697159051895142</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4941,7 +4941,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D266">
-        <v>1.270686626434326</v>
+        <v>0.8794986605644226</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4955,7 +4955,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D267">
-        <v>3.028221130371094</v>
+        <v>2.338858842849731</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4969,7 +4969,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D268">
-        <v>2.146689891815186</v>
+        <v>2.474985361099243</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4983,7 +4983,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D269">
-        <v>5.898808479309082</v>
+        <v>7.426249504089355</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4997,7 +4997,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D270">
-        <v>1.779907584190369</v>
+        <v>1.699331998825073</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5011,7 +5011,7 @@
         <v>2.5</v>
       </c>
       <c r="D271">
-        <v>2.023939609527588</v>
+        <v>2.385679721832275</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5025,7 +5025,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D272">
-        <v>2.012885093688965</v>
+        <v>1.936572074890137</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5039,7 +5039,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D273">
-        <v>2.472350120544434</v>
+        <v>2.722173452377319</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5053,7 +5053,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D274">
-        <v>2.083464384078979</v>
+        <v>2.37793231010437</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5067,7 +5067,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D275">
-        <v>1.517019748687744</v>
+        <v>1.146743655204773</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5081,7 +5081,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D276">
-        <v>1.207579374313354</v>
+        <v>1.429646492004395</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5095,7 +5095,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D277">
-        <v>2.196639537811279</v>
+        <v>2.626441717147827</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5109,7 +5109,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D278">
-        <v>2.559776306152344</v>
+        <v>2.256144285202026</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5123,7 +5123,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D279">
-        <v>0.9237669110298157</v>
+        <v>0.799652099609375</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5137,7 +5137,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D280">
-        <v>2.852427959442139</v>
+        <v>2.63533091545105</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5151,7 +5151,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D281">
-        <v>2.211419105529785</v>
+        <v>2.273972988128662</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5165,7 +5165,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D282">
-        <v>2.168082714080811</v>
+        <v>2.251178741455078</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5179,7 +5179,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D283">
-        <v>3.245402336120605</v>
+        <v>3.037378549575806</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5193,7 +5193,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D284">
-        <v>3.249792098999023</v>
+        <v>2.784406423568726</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5207,7 +5207,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D285">
-        <v>1.755446672439575</v>
+        <v>1.133931875228882</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5221,7 +5221,7 @@
         <v>2.5</v>
       </c>
       <c r="D286">
-        <v>2.329948425292969</v>
+        <v>2.593591690063477</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5235,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="D287">
-        <v>0.98052978515625</v>
+        <v>0.9090508222579956</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5249,7 +5249,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D288">
-        <v>1.126363635063171</v>
+        <v>1.306206941604614</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5263,7 +5263,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D289">
-        <v>3.035886287689209</v>
+        <v>2.562343120574951</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5277,7 +5277,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>1.142176151275635</v>
+        <v>1.022038459777832</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5291,7 +5291,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D291">
-        <v>1.663843512535095</v>
+        <v>0.8013454079627991</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5305,7 +5305,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D292">
-        <v>1.108001947402954</v>
+        <v>1.154907703399658</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5319,7 +5319,7 @@
         <v>13.5</v>
       </c>
       <c r="D293">
-        <v>4.882047176361084</v>
+        <v>4.116875648498535</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5333,7 +5333,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D294">
-        <v>3.473456382751465</v>
+        <v>2.74166464805603</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5347,7 +5347,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D295">
-        <v>6.158896923065186</v>
+        <v>6.372657775878906</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5361,7 +5361,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D296">
-        <v>1.761860847473145</v>
+        <v>1.666441202163696</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5375,7 +5375,7 @@
         <v>5</v>
       </c>
       <c r="D297">
-        <v>2.348779201507568</v>
+        <v>2.340825080871582</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5389,7 +5389,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D298">
-        <v>2.107511043548584</v>
+        <v>2.186362981796265</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5403,7 +5403,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D299">
-        <v>1.845299601554871</v>
+        <v>1.889932632446289</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5417,7 +5417,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D300">
-        <v>3.519449234008789</v>
+        <v>3.330455541610718</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5431,7 +5431,7 @@
         <v>8</v>
       </c>
       <c r="D301">
-        <v>10.41908073425293</v>
+        <v>8.034149169921875</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5445,7 +5445,7 @@
         <v>0.5</v>
       </c>
       <c r="D302">
-        <v>3.158310413360596</v>
+        <v>3.285639524459839</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5459,7 +5459,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D303">
-        <v>3.358749866485596</v>
+        <v>2.428023338317871</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5473,7 +5473,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D304">
-        <v>0.8376873135566711</v>
+        <v>0.7967709898948669</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5487,7 +5487,7 @@
         <v>3</v>
       </c>
       <c r="D305">
-        <v>3.179224491119385</v>
+        <v>2.870887517929077</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5501,7 +5501,7 @@
         <v>5</v>
       </c>
       <c r="D306">
-        <v>1.875668168067932</v>
+        <v>1.352827310562134</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5515,7 +5515,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D307">
-        <v>2.945315837860107</v>
+        <v>2.520214080810547</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5529,7 +5529,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D308">
-        <v>2.136423587799072</v>
+        <v>1.96045994758606</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5543,7 +5543,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D309">
-        <v>3.308768272399902</v>
+        <v>2.726685047149658</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5557,7 +5557,7 @@
         <v>1.5</v>
       </c>
       <c r="D310">
-        <v>0.8993386626243591</v>
+        <v>0.7932057976722717</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5571,7 +5571,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D311">
-        <v>1.09791088104248</v>
+        <v>1.386983871459961</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5585,7 +5585,7 @@
         <v>0.5</v>
       </c>
       <c r="D312">
-        <v>1.052462697029114</v>
+        <v>0.9777661561965942</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5599,7 +5599,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D313">
-        <v>1.36837375164032</v>
+        <v>2.541208982467651</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5613,7 +5613,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D314">
-        <v>1.356646299362183</v>
+        <v>1.618732213973999</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5627,7 +5627,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D315">
-        <v>2.201051235198975</v>
+        <v>2.762367010116577</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5641,7 +5641,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D316">
-        <v>1.626159429550171</v>
+        <v>0.8737940788269043</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -5655,7 +5655,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D317">
-        <v>4.765082359313965</v>
+        <v>4.087381839752197</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -5669,7 +5669,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D318">
-        <v>4.309971809387207</v>
+        <v>4.666882038116455</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5683,7 +5683,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D319">
-        <v>2.088915824890137</v>
+        <v>2.558567047119141</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -5697,7 +5697,7 @@
         <v>4</v>
       </c>
       <c r="D320">
-        <v>1.115519404411316</v>
+        <v>1.360005140304565</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5711,7 +5711,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D321">
-        <v>2.409341335296631</v>
+        <v>2.769688844680786</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5725,7 +5725,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D322">
-        <v>1.339690327644348</v>
+        <v>1.230507850646973</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5739,7 +5739,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D323">
-        <v>2.340869903564453</v>
+        <v>2.514430284500122</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -5753,7 +5753,7 @@
         <v>2</v>
       </c>
       <c r="D324">
-        <v>1.442921161651611</v>
+        <v>0.8517695665359497</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -5767,7 +5767,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D325">
-        <v>1.665109038352966</v>
+        <v>1.434707164764404</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5781,7 +5781,7 @@
         <v>6</v>
       </c>
       <c r="D326">
-        <v>4.31865930557251</v>
+        <v>5.108529567718506</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5795,7 +5795,7 @@
         <v>1.5</v>
       </c>
       <c r="D327">
-        <v>1.077136039733887</v>
+        <v>1.245367765426636</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -5809,7 +5809,7 @@
         <v>3.5</v>
       </c>
       <c r="D328">
-        <v>1.72051990032196</v>
+        <v>2.240164756774902</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5823,7 +5823,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D329">
-        <v>2.106148242950439</v>
+        <v>2.886292457580566</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5837,7 +5837,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D330">
-        <v>1.436422348022461</v>
+        <v>0.8062847852706909</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5851,7 +5851,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D331">
-        <v>2.587425708770752</v>
+        <v>2.788305282592773</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5865,7 +5865,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D332">
-        <v>2.482262134552002</v>
+        <v>2.575007677078247</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5879,7 +5879,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D333">
-        <v>1.68931770324707</v>
+        <v>0.8121572732925415</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5893,7 +5893,7 @@
         <v>7.5</v>
       </c>
       <c r="D334">
-        <v>3.622350692749023</v>
+        <v>3.674514532089233</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5907,7 +5907,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D335">
-        <v>1.142106890678406</v>
+        <v>1.333321571350098</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5921,7 +5921,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D336">
-        <v>2.610875606536865</v>
+        <v>2.531867742538452</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5935,7 +5935,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D337">
-        <v>0.9926056861877441</v>
+        <v>0.8140367865562439</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5949,7 +5949,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D338">
-        <v>1.996605038642883</v>
+        <v>1.527415037155151</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5963,7 +5963,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D339">
-        <v>1.064179182052612</v>
+        <v>1.25654673576355</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5977,7 +5977,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D340">
-        <v>4.099757671356201</v>
+        <v>2.93128514289856</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5991,7 +5991,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D341">
-        <v>0.8491787314414978</v>
+        <v>0.8874281048774719</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6005,7 +6005,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D342">
-        <v>2.136965751647949</v>
+        <v>2.039167404174805</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6019,7 +6019,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D343">
-        <v>1.546555876731873</v>
+        <v>1.130550980567932</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6033,7 +6033,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D344">
-        <v>2.23121976852417</v>
+        <v>2.320712804794312</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6047,7 +6047,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D345">
-        <v>2.233349800109863</v>
+        <v>1.857256174087524</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6061,7 +6061,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D346">
-        <v>1.416305065155029</v>
+        <v>0.8111130595207214</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6075,7 +6075,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D347">
-        <v>3.825154781341553</v>
+        <v>3.801511526107788</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6089,7 +6089,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D348">
-        <v>2.990450859069824</v>
+        <v>2.418148994445801</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6103,7 +6103,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D349">
-        <v>3.014238357543945</v>
+        <v>2.650407791137695</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6117,7 +6117,7 @@
         <v>4</v>
       </c>
       <c r="D350">
-        <v>3.54004430770874</v>
+        <v>2.926429271697998</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6131,7 +6131,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D351">
-        <v>1.059944152832031</v>
+        <v>1.101205468177795</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6145,7 +6145,7 @@
         <v>3</v>
       </c>
       <c r="D352">
-        <v>2.32804536819458</v>
+        <v>2.608107566833496</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6159,7 +6159,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D353">
-        <v>1.574871063232422</v>
+        <v>1.95125675201416</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6173,7 +6173,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D354">
-        <v>1.04893958568573</v>
+        <v>0.8184641003608704</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6187,7 +6187,7 @@
         <v>4</v>
       </c>
       <c r="D355">
-        <v>2.483585357666016</v>
+        <v>2.600560903549194</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6201,7 +6201,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D356">
-        <v>3.803817749023438</v>
+        <v>5.2381591796875</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6215,7 +6215,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D357">
-        <v>4.458055973052979</v>
+        <v>3.967562675476074</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6229,7 +6229,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D358">
-        <v>2.117578029632568</v>
+        <v>2.39751148223877</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6243,7 +6243,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D359">
-        <v>2.880626678466797</v>
+        <v>2.332545042037964</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6257,7 +6257,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D360">
-        <v>0.9443841576576233</v>
+        <v>1.103662490844727</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6271,7 +6271,7 @@
         <v>4.5</v>
       </c>
       <c r="D361">
-        <v>2.16616415977478</v>
+        <v>2.385968208312988</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6285,7 +6285,7 @@
         <v>2.5</v>
       </c>
       <c r="D362">
-        <v>2.136120796203613</v>
+        <v>1.960158109664917</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6299,7 +6299,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D363">
-        <v>3.414050102233887</v>
+        <v>2.713803291320801</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6313,7 +6313,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D364">
-        <v>0.9310282468795776</v>
+        <v>2.216401100158691</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6327,7 +6327,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D365">
-        <v>6.670570850372314</v>
+        <v>2.898550033569336</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6341,7 +6341,7 @@
         <v>2.5</v>
       </c>
       <c r="D366">
-        <v>2.216827869415283</v>
+        <v>2.472766876220703</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6355,7 +6355,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D367">
-        <v>1.835841298103333</v>
+        <v>1.013132333755493</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6369,7 +6369,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D368">
-        <v>6.198265552520752</v>
+        <v>4.467720031738281</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6383,7 +6383,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D369">
-        <v>1.02063250541687</v>
+        <v>0.8174262642860413</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6397,7 +6397,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D370">
-        <v>8.426353454589844</v>
+        <v>7.094343662261963</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6411,7 +6411,7 @@
         <v>3.5</v>
       </c>
       <c r="D371">
-        <v>3.46672248840332</v>
+        <v>2.895119667053223</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6425,7 +6425,7 @@
         <v>0.5</v>
       </c>
       <c r="D372">
-        <v>1.10237193107605</v>
+        <v>1.194541454315186</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6439,7 +6439,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D373">
-        <v>2.81343936920166</v>
+        <v>1.96573281288147</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6453,7 +6453,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D374">
-        <v>1.101841449737549</v>
+        <v>1.338294744491577</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6467,7 +6467,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D375">
-        <v>3.050151824951172</v>
+        <v>2.504931449890137</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6481,7 +6481,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D376">
-        <v>1.154550790786743</v>
+        <v>1.372665882110596</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6495,7 +6495,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D377">
-        <v>0.9769601821899414</v>
+        <v>0.9602463245391846</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6509,7 +6509,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D378">
-        <v>3.481167793273926</v>
+        <v>2.895500421524048</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6523,7 +6523,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D379">
-        <v>2.586398601531982</v>
+        <v>2.952805757522583</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6537,7 +6537,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D380">
-        <v>1.698582291603088</v>
+        <v>1.848234891891479</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6551,7 +6551,7 @@
         <v>2</v>
       </c>
       <c r="D381">
-        <v>1.132803440093994</v>
+        <v>1.36291766166687</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6565,7 +6565,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D382">
-        <v>1.35555100440979</v>
+        <v>1.801275014877319</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6579,7 +6579,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D383">
-        <v>1.191290020942688</v>
+        <v>1.349028825759888</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6593,7 +6593,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D384">
-        <v>2.344614028930664</v>
+        <v>2.556458473205566</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6607,7 +6607,7 @@
         <v>3.5</v>
       </c>
       <c r="D385">
-        <v>1.792080760002136</v>
+        <v>1.328951120376587</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -6621,7 +6621,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D386">
-        <v>3.083455085754395</v>
+        <v>2.019205570220947</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -6635,7 +6635,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D387">
-        <v>3.387550354003906</v>
+        <v>2.582458257675171</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -6649,7 +6649,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D388">
-        <v>0.8815073370933533</v>
+        <v>1.105270385742188</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -6663,7 +6663,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D389">
-        <v>1.39204728603363</v>
+        <v>1.680718660354614</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -6677,7 +6677,7 @@
         <v>2.5</v>
       </c>
       <c r="D390">
-        <v>2.143095016479492</v>
+        <v>2.300524711608887</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -6691,7 +6691,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D391">
-        <v>1.089430212974548</v>
+        <v>1.198218107223511</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -6705,7 +6705,7 @@
         <v>1.5</v>
       </c>
       <c r="D392">
-        <v>1.242688536643982</v>
+        <v>1.035307168960571</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -6719,7 +6719,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D393">
-        <v>2.13115119934082</v>
+        <v>2.224167585372925</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -6733,7 +6733,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D394">
-        <v>1.064416885375977</v>
+        <v>0.8367950320243835</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -6747,7 +6747,7 @@
         <v>1.5</v>
       </c>
       <c r="D395">
-        <v>2.539268016815186</v>
+        <v>2.398404598236084</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -6761,7 +6761,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D396">
-        <v>1.181763410568237</v>
+        <v>1.34298038482666</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -6775,7 +6775,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D397">
-        <v>2.407916307449341</v>
+        <v>2.571927309036255</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -6789,7 +6789,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D398">
-        <v>3.239694118499756</v>
+        <v>3.262903690338135</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -6803,7 +6803,7 @@
         <v>1</v>
       </c>
       <c r="D399">
-        <v>1.097613453865051</v>
+        <v>1.362594842910767</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -6817,7 +6817,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D400">
-        <v>3.410799026489258</v>
+        <v>2.863767385482788</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -6831,7 +6831,7 @@
         <v>4</v>
       </c>
       <c r="D401">
-        <v>3.273709774017334</v>
+        <v>3.081049919128418</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6845,7 +6845,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D402">
-        <v>1.179444193840027</v>
+        <v>1.269793033599854</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6859,7 +6859,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D403">
-        <v>2.680576324462891</v>
+        <v>2.778547525405884</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6873,7 +6873,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D404">
-        <v>2.16567325592041</v>
+        <v>2.264276742935181</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6887,7 +6887,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D405">
-        <v>0.9597248435020447</v>
+        <v>0.866249144077301</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6901,7 +6901,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D406">
-        <v>2.911618232727051</v>
+        <v>2.529083967208862</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6915,7 +6915,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D407">
-        <v>1.160451650619507</v>
+        <v>1.41752552986145</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6929,7 +6929,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D408">
-        <v>3.267650127410889</v>
+        <v>2.717442035675049</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6943,7 +6943,7 @@
         <v>4.5</v>
       </c>
       <c r="D409">
-        <v>1.108581781387329</v>
+        <v>1.408534288406372</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6957,7 +6957,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D410">
-        <v>1.030191540718079</v>
+        <v>0.8189663290977478</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6971,7 +6971,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D411">
-        <v>1.505113363265991</v>
+        <v>1.268468856811523</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6985,7 +6985,7 @@
         <v>6.5</v>
       </c>
       <c r="D412">
-        <v>3.777683258056641</v>
+        <v>3.598176240921021</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6999,7 +6999,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D413">
-        <v>3.476758003234863</v>
+        <v>4.024937629699707</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7013,7 +7013,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D414">
-        <v>2.526909828186035</v>
+        <v>2.280125856399536</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7027,7 +7027,7 @@
         <v>3.5</v>
       </c>
       <c r="D415">
-        <v>2.253376483917236</v>
+        <v>2.589301347732544</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7041,7 +7041,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D416">
-        <v>8.323297500610352</v>
+        <v>7.150259971618652</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7055,7 +7055,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D417">
-        <v>3.688452243804932</v>
+        <v>3.437985420227051</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7069,7 +7069,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D418">
-        <v>2.141545295715332</v>
+        <v>2.479388475418091</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7083,7 +7083,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D419">
-        <v>0.8135360479354858</v>
+        <v>0.8419374823570251</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7097,7 +7097,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D420">
-        <v>1.365741014480591</v>
+        <v>0.9131054878234863</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7111,7 +7111,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D421">
-        <v>2.743901252746582</v>
+        <v>2.555998563766479</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7125,7 +7125,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D422">
-        <v>2.417291164398193</v>
+        <v>1.568053483963013</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7139,7 +7139,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D423">
-        <v>3.254480838775635</v>
+        <v>2.546961069107056</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7153,7 +7153,7 @@
         <v>1</v>
       </c>
       <c r="D424">
-        <v>1.029663801193237</v>
+        <v>0.9967116117477417</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7167,7 +7167,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D425">
-        <v>0.9464046955108643</v>
+        <v>0.8416096568107605</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7181,7 +7181,7 @@
         <v>5</v>
       </c>
       <c r="D426">
-        <v>3.27271556854248</v>
+        <v>3.316807508468628</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7195,7 +7195,7 @@
         <v>0.5</v>
       </c>
       <c r="D427">
-        <v>0.8409203290939331</v>
+        <v>1.343040227890015</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7209,7 +7209,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D428">
-        <v>1.130447626113892</v>
+        <v>1.193390369415283</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7223,7 +7223,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>3.377800464630127</v>
+        <v>2.668466329574585</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7237,7 +7237,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D430">
-        <v>2.952983379364014</v>
+        <v>3.204145669937134</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7251,7 +7251,7 @@
         <v>0.5</v>
       </c>
       <c r="D431">
-        <v>1.199323058128357</v>
+        <v>1.375105142593384</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7265,7 +7265,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D432">
-        <v>2.217760562896729</v>
+        <v>2.671835660934448</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7279,7 +7279,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D433">
-        <v>1.11718225479126</v>
+        <v>1.423341274261475</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7293,7 +7293,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D434">
-        <v>1.198782801628113</v>
+        <v>1.387763261795044</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7307,7 +7307,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D435">
-        <v>3.783179759979248</v>
+        <v>3.64274525642395</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7321,7 +7321,7 @@
         <v>0.5</v>
       </c>
       <c r="D436">
-        <v>2.608182430267334</v>
+        <v>2.636460542678833</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7335,7 +7335,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D437">
-        <v>0.8450388312339783</v>
+        <v>0.8758642673492432</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7349,7 +7349,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D438">
-        <v>1.090422391891479</v>
+        <v>1.136136174201965</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7363,7 +7363,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D439">
-        <v>1.937294840812683</v>
+        <v>2.107396364212036</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7377,7 +7377,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D440">
-        <v>1.096255540847778</v>
+        <v>1.190436005592346</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7391,7 +7391,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D441">
-        <v>1.07038950920105</v>
+        <v>1.051847696304321</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7405,7 +7405,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D442">
-        <v>0.8135360479354858</v>
+        <v>0.7879031896591187</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7419,7 +7419,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D443">
-        <v>3.468800067901611</v>
+        <v>4.375054836273193</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7433,7 +7433,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D444">
-        <v>3.391765117645264</v>
+        <v>2.926547765731812</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7447,7 +7447,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D445">
-        <v>1.504562616348267</v>
+        <v>1.515744924545288</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7461,7 +7461,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D446">
-        <v>1.957807064056396</v>
+        <v>1.883150815963745</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7475,7 +7475,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D447">
-        <v>1.13041889667511</v>
+        <v>1.16610324382782</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7489,7 +7489,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D448">
-        <v>2.500623226165771</v>
+        <v>4.560220241546631</v>
       </c>
     </row>
   </sheetData>
